--- a/dataset_t6_grouped/results2/G3/G3_T1829_W0042F0002T0006Z000C1N21_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T1829_W0042F0002T0006Z000C1N21_analysis.xlsx
@@ -480,10 +480,10 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>34.43514303066074</v>
+        <v>5.59571074248237</v>
       </c>
       <c r="D2" t="n">
-        <v>31.06338419179122</v>
+        <v>5.047799931166074</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
